--- a/files/R01-R69全节点业务验收测试包/S03_焊缝返修与热处理/S03_S03-PWHT-RECORD-001_TEST-S03-009_热处理曲线与硬度记录.xlsx
+++ b/files/R01-R69全节点业务验收测试包/S03_焊缝返修与热处理/S03_S03-PWHT-RECORD-001_TEST-S03-009_热处理曲线与硬度记录.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="热处理曲线" sheetId="1" r:id="R5b6593ebf4b6416a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="硬度记录" sheetId="2" r:id="R039efea854df44df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="热处理曲线" sheetId="1" r:id="Rab2c52197fe84db3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="硬度记录" sheetId="2" r:id="R49649c57a5584cc4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43,7 +43,7 @@
       <x:name val="Arial Unicode MS"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -60,8 +60,13 @@
         <x:fgColor rgb="FFFCE8E6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3F1"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="17">
     <x:border/>
     <x:border>
       <x:left/>
@@ -90,12 +95,64 @@
     <x:border>
       <x:right/>
       <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="69">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -187,6 +244,70 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -238,6 +359,70 @@
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="876300"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="ec64ed29-de04-49e0-a6e0-5e704f576ec4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re6d5444a215048bd"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="876300"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="4c935fa9-1d82-4ebb-b3f3-82463b192a7f"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R784dd2ec6ec7430a"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -439,6 +624,7 @@
     <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="18" hidden="0" customHeight="1">
@@ -448,6 +634,7 @@
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
       <x:c r="D1" s="4"/>
+      <x:c r="E1" s="4"/>
     </x:row>
     <x:row r="2" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A2" s="9" t="str">
@@ -456,6 +643,7 @@
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
       <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
     </x:row>
     <x:row r="3"/>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -767,11 +955,43 @@
       </x:c>
     </x:row>
     <x:row r="26"/>
-    <x:row r="27"/>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="60" t="str">
+        <x:v>电子签署（测试）｜工程质量测试专用章</x:v>
+      </x:c>
+      <x:c r="B27" s="61"/>
+      <x:c r="C27" s="61"/>
+      <x:c r="D27" s="61"/>
+      <x:c r="E27" s="62"/>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="63"/>
+      <x:c r="B28" s="64"/>
+      <x:c r="C28" s="64"/>
+      <x:c r="D28" s="64"/>
+      <x:c r="E28" s="65"/>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="63"/>
+      <x:c r="B29" s="64"/>
+      <x:c r="C29" s="64"/>
+      <x:c r="D29" s="64"/>
+      <x:c r="E29" s="65"/>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="66"/>
+      <x:c r="B30" s="67"/>
+      <x:c r="C30" s="67"/>
+      <x:c r="D30" s="67"/>
+      <x:c r="E30" s="68"/>
+    </x:row>
+    <x:row r="31"/>
+    <x:row r="32"/>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A27:C27"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A5:D25">
     <x:cfRule type="expression" dxfId="0" priority="1">
@@ -782,6 +1002,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3647f932924d4cce"/>
 </x:worksheet>
 </file>
 
@@ -1037,11 +1258,43 @@
       </x:c>
     </x:row>
     <x:row r="17"/>
-    <x:row r="18"/>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="60" t="str">
+        <x:v>电子签署（测试）｜工程质量测试专用章</x:v>
+      </x:c>
+      <x:c r="B18" s="61"/>
+      <x:c r="C18" s="61"/>
+      <x:c r="D18" s="61"/>
+      <x:c r="E18" s="62"/>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="63"/>
+      <x:c r="B19" s="64"/>
+      <x:c r="C19" s="64"/>
+      <x:c r="D19" s="64"/>
+      <x:c r="E19" s="65"/>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="63"/>
+      <x:c r="B20" s="64"/>
+      <x:c r="C20" s="64"/>
+      <x:c r="D20" s="64"/>
+      <x:c r="E20" s="65"/>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="66"/>
+      <x:c r="B21" s="67"/>
+      <x:c r="C21" s="67"/>
+      <x:c r="D21" s="67"/>
+      <x:c r="E21" s="68"/>
+    </x:row>
+    <x:row r="22"/>
+    <x:row r="23"/>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A18:C18"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A5:E16">
     <x:cfRule type="expression" dxfId="2" priority="1">
@@ -1052,5 +1305,6 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f920c1b52e64d86"/>
 </x:worksheet>
 </file>